--- a/agenda_site_separada_por_meses (2).xlsx
+++ b/agenda_site_separada_por_meses (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\CRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD6F635-AE53-45C1-AF58-0898B0F93773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5D47BA-3AA1-493A-BAB3-E6E4A892E6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="172">
   <si>
     <t>MÊS</t>
   </si>
@@ -93,12 +93,6 @@
     <t>Acupuntura</t>
   </si>
   <si>
-    <t>2 meses e 1/2</t>
-  </si>
-  <si>
-    <t>Meridianos e Localização de pontos</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -138,9 +132,6 @@
     <t>Segunda e Quarta</t>
   </si>
   <si>
-    <t>Auriculoterapia</t>
-  </si>
-  <si>
     <t>Segunda</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
     <t>FDS</t>
   </si>
   <si>
-    <t>Massagem antiestresse - antigo</t>
-  </si>
-  <si>
     <t>15 dias</t>
   </si>
   <si>
@@ -180,9 +168,6 @@
     <t>Drenagem linfática pós-operatória</t>
   </si>
   <si>
-    <t>Drenagem Linfática Pré e Pós operatória</t>
-  </si>
-  <si>
     <t>16/05/2026</t>
   </si>
   <si>
@@ -204,9 +189,6 @@
     <t>Terapias holísticas - Naturopatia</t>
   </si>
   <si>
-    <t>Massagem do in - antigo</t>
-  </si>
-  <si>
     <t>2ºFDS</t>
   </si>
   <si>
@@ -231,18 +213,12 @@
     <t>23/05/2026</t>
   </si>
   <si>
-    <t>Massagem ayurvédica - antigo - I</t>
-  </si>
-  <si>
     <t>4ºFDS</t>
   </si>
   <si>
     <t>Craniopuntura japonesa</t>
   </si>
   <si>
-    <t>Meridianos e localização de pontos I</t>
-  </si>
-  <si>
     <t>26/05/2026</t>
   </si>
   <si>
@@ -258,9 +234,6 @@
     <t>29/05/2026</t>
   </si>
   <si>
-    <t>Reflexologia podal</t>
-  </si>
-  <si>
     <t>sexta</t>
   </si>
   <si>
@@ -276,9 +249,6 @@
     <t>3ºFDS</t>
   </si>
   <si>
-    <t>Mapa da anatomia sutil (chakras e corpos sutis)</t>
-  </si>
-  <si>
     <t>01/06/2026</t>
   </si>
   <si>
@@ -465,18 +435,6 @@
     <t>31/08/2026</t>
   </si>
   <si>
-    <t>15/05/2027</t>
-  </si>
-  <si>
-    <t>Moxaterapia, Ventosaterapia e Gua Sha</t>
-  </si>
-  <si>
-    <t>18/05/2027</t>
-  </si>
-  <si>
-    <t>Avaliação final - 27.05.25</t>
-  </si>
-  <si>
     <t>01/06/2027</t>
   </si>
   <si>
@@ -559,6 +517,30 @@
   </si>
   <si>
     <t>Sáb. 08:30</t>
+  </si>
+  <si>
+    <t>Jornada das Terapias holístcas</t>
+  </si>
+  <si>
+    <t>Pós graduação em Acupuntura Premiun</t>
+  </si>
+  <si>
+    <t>Jornada em Massoterapia Integrativa</t>
+  </si>
+  <si>
+    <t>Shiatsu</t>
+  </si>
+  <si>
+    <t>Jornada das Terapias Holisticas - Naturopatia</t>
+  </si>
+  <si>
+    <t>12 mês</t>
+  </si>
+  <si>
+    <t>18 mês</t>
+  </si>
+  <si>
+    <t>05/05/20+A2:F10026</t>
   </si>
 </sst>
 </file>
@@ -690,8 +672,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela_AgendaMaioaAgosto" displayName="Tabela_AgendaMaioaAgosto" ref="A1:F176">
-  <autoFilter ref="A1:F176" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela_AgendaMaioaAgosto" displayName="Tabela_AgendaMaioaAgosto" ref="A1:F110">
+  <autoFilter ref="A1:F110" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="DATA"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="CURSO"/>
@@ -1133,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1163,9 +1145,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>13</v>
@@ -1188,10 +1170,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>15</v>
@@ -1205,30 +1187,30 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>20</v>
@@ -1237,167 +1219,167 @@
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>17</v>
@@ -1405,39 +1387,39 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
@@ -1445,19 +1427,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>17</v>
@@ -1465,256 +1447,264 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>14</v>
@@ -1723,47 +1713,47 @@
         <v>54</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>17</v>
@@ -1771,479 +1761,471 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>42</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>56</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>17</v>
@@ -2251,39 +2233,39 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>17</v>
@@ -2291,39 +2273,37 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>17</v>
@@ -2331,30 +2311,30 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>20</v>
@@ -2366,172 +2346,182 @@
         <v>16</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F67" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F68" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>17</v>
@@ -2539,59 +2529,57 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>17</v>
@@ -2599,139 +2587,135 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>17</v>
@@ -2739,19 +2723,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>17</v>
@@ -2759,1795 +2743,539 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E94" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="E95" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F96" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F97" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>56</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>56</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F101" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F104" s="4"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F105" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F108" s="4"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E112" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F112" s="4"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F127" s="4"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F130" s="4"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F131" s="4"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F133" s="4"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F134" s="4"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F135" s="4"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F136" s="4"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F148" s="4"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F149" s="4"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" s="4"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" s="4"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F155" s="4"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E156" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F156" s="4"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F157" s="4"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E158" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F158" s="4"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F159" s="4"/>
-    </row>
-    <row r="160" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F160" s="4"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D161" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F161" s="4"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F162" s="4"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="4"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F164" s="4"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F165" s="4"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F166" s="4"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F167" s="4"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F168" s="4"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F169" s="4"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F170" s="4"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F171" s="4"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F172" s="4"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F173" s="4"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F174" s="4"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F175" s="4"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F176" s="4"/>
+      <c r="F110" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4597,7 +3325,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>15</v>
@@ -4634,7 +3362,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>20</v>
@@ -4646,7 +3374,7 @@
         <v>0.375</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4654,7 +3382,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>20</v>
@@ -4666,21 +3394,21 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E6" s="5">
         <v>0.79166666666666663</v>
@@ -4691,176 +3419,176 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E7" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E8" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E9" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E11" s="9">
         <v>0.375</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="E12" s="5">
         <v>0.375</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" s="5">
         <v>0.375</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9">
         <v>0.375</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="5">
         <v>0.79166666666666663</v>
@@ -4871,136 +3599,136 @@
     </row>
     <row r="16" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" s="9">
         <v>0.375</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" s="5">
         <v>0.375</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E18" s="9">
         <v>0.58333333333333337</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E19" s="5">
         <v>0.58333333333333337</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E20" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E21" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5">
         <v>0.79166666666666663</v>
@@ -5011,90 +3739,90 @@
     </row>
     <row r="23" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>20</v>
@@ -5111,99 +3839,99 @@
     </row>
     <row r="28" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E29" s="9">
         <v>0.79166666666666663</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E30" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>17</v>
@@ -5211,30 +3939,30 @@
     </row>
     <row r="33" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>20</v>
@@ -5246,12 +3974,12 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>21</v>
@@ -5266,41 +3994,41 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E36" s="9">
         <v>0.375</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" s="5">
         <v>0.375</v>
@@ -5311,16 +4039,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E38" s="5">
         <v>0.375</v>
@@ -5331,82 +4059,82 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5452,56 +4180,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E4" s="5">
         <v>0.58333333333333337</v>
@@ -5512,16 +4240,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E5" s="5">
         <v>0.58333333333333337</v>
@@ -5532,16 +4260,16 @@
     </row>
     <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="5">
         <v>0.58333333333333337</v>
@@ -5552,16 +4280,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="5">
         <v>0.58333333333333337</v>
@@ -5572,7 +4300,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>13</v>
@@ -5592,7 +4320,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
@@ -5612,10 +4340,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>20</v>
@@ -5632,16 +4360,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5">
         <v>0.375</v>
@@ -5652,16 +4380,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5">
         <v>0.375</v>
@@ -5672,16 +4400,16 @@
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E13" s="5">
         <v>0.375</v>
@@ -5690,16 +4418,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E14" s="5">
         <v>0.375</v>
@@ -5708,16 +4436,16 @@
     </row>
     <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E15" s="5">
         <v>0.58333333333333337</v>
@@ -5726,16 +4454,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" s="5">
         <v>0.58333333333333337</v>
@@ -5744,16 +4472,16 @@
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" s="5">
         <v>0.79166666666666663</v>
@@ -5762,16 +4490,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E18" s="5">
         <v>0.79166666666666663</v>
@@ -5780,16 +4508,16 @@
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E19" s="5">
         <v>0.79166666666666663</v>
@@ -5800,16 +4528,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E20" s="5">
         <v>0.79166666666666663</v>
@@ -5820,16 +4548,16 @@
     </row>
     <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" s="5">
         <v>0.79166666666666663</v>
@@ -5840,16 +4568,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5">
         <v>0.79166666666666663</v>
@@ -5860,16 +4588,16 @@
     </row>
     <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E23" s="5">
         <v>0.375</v>
@@ -5880,16 +4608,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E24" s="5">
         <v>0.375</v>
@@ -5900,7 +4628,7 @@
     </row>
     <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>21</v>
@@ -5909,50 +4637,50 @@
         <v>14</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>17</v>
@@ -5960,19 +4688,19 @@
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>17</v>
@@ -5980,19 +4708,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>17</v>
@@ -6000,10 +4728,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>20</v>
@@ -6020,156 +4748,156 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E31" s="5">
         <v>0.375</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" s="5">
         <v>0.375</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E38" s="5">
         <v>0.375</v>
@@ -6180,16 +4908,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E39" s="5">
         <v>0.375</v>
@@ -6200,16 +4928,16 @@
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E40" s="5">
         <v>0.375</v>
@@ -6218,16 +4946,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E41" s="5">
         <v>0.375</v>
@@ -6236,16 +4964,16 @@
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E42" s="5">
         <v>0.58333333333333337</v>
@@ -6254,16 +4982,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E43" s="5">
         <v>0.58333333333333337</v>
@@ -6272,16 +5000,16 @@
     </row>
     <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E44" s="5">
         <v>0.79166666666666663</v>
@@ -6290,16 +5018,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E45" s="5">
         <v>0.79166666666666663</v>
@@ -6308,76 +5036,76 @@
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E49" s="5">
         <v>0.375</v>
@@ -6386,16 +5114,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E50" s="5">
         <v>0.375</v>
@@ -6404,16 +5132,16 @@
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E51" s="5">
         <v>0.58333333333333337</v>
@@ -6422,16 +5150,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E52" s="5">
         <v>0.58333333333333337</v>
@@ -6440,16 +5168,16 @@
     </row>
     <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E53" s="5">
         <v>0.79166666666666663</v>
@@ -6458,16 +5186,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E54" s="5">
         <v>0.79166666666666663</v>
@@ -6476,37 +5204,37 @@
     </row>
     <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F56" s="4"/>
     </row>
@@ -6552,73 +5280,73 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -6664,7 +5392,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>21</v>
@@ -6673,86 +5401,86 @@
         <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>17</v>
@@ -6760,19 +5488,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>17</v>
@@ -6780,19 +5508,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>17</v>
@@ -6800,19 +5528,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>17</v>
@@ -6820,19 +5548,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>17</v>
@@ -6840,16 +5568,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>16</v>
@@ -6858,10 +5586,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>20</v>
@@ -6878,7 +5606,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
@@ -6890,18 +5618,18 @@
         <v>15</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>20</v>
@@ -6910,15 +5638,15 @@
         <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>21</v>
@@ -6933,15 +5661,15 @@
         <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>20</v>
@@ -6953,35 +5681,35 @@
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>20</v>
@@ -6990,24 +5718,24 @@
         <v>15</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>16</v>
@@ -7018,16 +5746,16 @@
     </row>
     <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -7038,19 +5766,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>17</v>
@@ -7058,19 +5786,19 @@
     </row>
     <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>17</v>
@@ -7078,97 +5806,97 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>17</v>
@@ -7176,19 +5904,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>17</v>
@@ -7196,46 +5924,46 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>20</v>
@@ -7244,7 +5972,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>17</v>
@@ -7252,52 +5980,52 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>16</v>
@@ -7306,16 +6034,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>16</v>
@@ -7324,76 +6052,76 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>16</v>
@@ -7404,16 +6132,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>16</v>
@@ -7424,19 +6152,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>17</v>
@@ -7444,19 +6172,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>17</v>
@@ -7464,59 +6192,59 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>17</v>
@@ -7524,19 +6252,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>17</v>
@@ -7544,88 +6272,88 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>16</v>
@@ -7634,16 +6362,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>16</v>
@@ -7652,124 +6380,124 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>16</v>
@@ -7778,16 +6506,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>16</v>
